--- a/ZonasEscolares/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
+++ b/ZonasEscolares/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -503,12 +503,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -555,12 +555,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -659,12 +659,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -763,12 +763,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -867,12 +867,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LA_CONVENCION</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SANTA_ANA</t>
+          <t>SANTA ANA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
+++ b/ZonasEscolares/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>50226 LA INMACULADA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.863071</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-72.6953</v>
-      </c>
-      <c r="I2" t="n">
-        <v>707</v>
-      </c>
-      <c r="J2" t="n">
-        <v>46</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.863071</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-72.6953</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>50227 SAN FRANCISCO JAVIER</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.85715</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-72.69539</v>
-      </c>
-      <c r="I3" t="n">
-        <v>378</v>
-      </c>
-      <c r="J3" t="n">
-        <v>27</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.85715</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-72.69539</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>50230</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.868114</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-72.691863</v>
-      </c>
-      <c r="I4" t="n">
-        <v>348</v>
-      </c>
-      <c r="J4" t="n">
-        <v>21</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.868114</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-72.691863</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>50236 SANTA ANA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.87124</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-72.693727</v>
-      </c>
-      <c r="I5" t="n">
-        <v>883</v>
-      </c>
-      <c r="J5" t="n">
-        <v>50</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.87124</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-72.693727</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>883</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>51027 JUAN DE LA CRUZ MONTES SALAS</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.862064</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-72.69234899999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1204</v>
-      </c>
-      <c r="J6" t="n">
-        <v>63</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.862064</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-72.692349</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>51028 EL ROSARIO</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.868313</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-72.69593</v>
-      </c>
-      <c r="I7" t="n">
-        <v>473</v>
-      </c>
-      <c r="J7" t="n">
-        <v>23</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.868313</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-72.69593</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>51076</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.86838</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-72.69906</v>
-      </c>
-      <c r="I8" t="n">
-        <v>238</v>
-      </c>
-      <c r="J8" t="n">
-        <v>15</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.86838</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-72.69906</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>501156 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.88148</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-72.69315</v>
-      </c>
-      <c r="I9" t="n">
-        <v>254</v>
-      </c>
-      <c r="J9" t="n">
-        <v>18</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.88148</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-72.69315</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>INA 67</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.856707</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-72.69593</v>
-      </c>
-      <c r="I10" t="n">
-        <v>209</v>
-      </c>
-      <c r="J10" t="n">
-        <v>25</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.856707</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-72.69593</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>LA CONVENCION</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.857625</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-72.693555</v>
-      </c>
-      <c r="I11" t="n">
-        <v>800</v>
-      </c>
-      <c r="J11" t="n">
-        <v>54</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.857625</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-72.693555</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>MANCO II</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.865258</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-72.69233699999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>953</v>
-      </c>
-      <c r="J12" t="n">
-        <v>58</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.865258</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-72.692337</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>BUEN MAESTRO</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.86731</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-72.69571000000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>265</v>
-      </c>
-      <c r="J13" t="n">
-        <v>13</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.86731</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-72.69571</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>LA SALLE</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.86231</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-72.69904</v>
-      </c>
-      <c r="I14" t="n">
-        <v>665</v>
-      </c>
-      <c r="J14" t="n">
-        <v>32</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.86231</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-72.69904</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>50847</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.608377</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-72.946645</v>
-      </c>
-      <c r="I15" t="n">
-        <v>10</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.608377</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-72.946645</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>38704</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.7931</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-73.6217</v>
-      </c>
-      <c r="I16" t="n">
-        <v>638</v>
-      </c>
-      <c r="J16" t="n">
-        <v>39</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.7931</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-73.6217</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>50985 ALTO SALKANTAY</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-13.228343</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-72.628621</v>
-      </c>
-      <c r="I17" t="n">
-        <v>209</v>
-      </c>
-      <c r="J17" t="n">
-        <v>26</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-13.228343</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-72.628621</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>RIQCHARIY WAYNA</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.629164</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-72.97471899999999</v>
-      </c>
-      <c r="I18" t="n">
-        <v>242</v>
-      </c>
-      <c r="J18" t="n">
-        <v>20</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.629164</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-72.974719</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>PITIRINKENI</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.243557</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-73.866653</v>
-      </c>
-      <c r="I19" t="n">
-        <v>204</v>
-      </c>
-      <c r="J19" t="n">
-        <v>15</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.243557</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-73.866653</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>TALENTOS DE PITAGORAS</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.87354</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-72.6949</v>
-      </c>
-      <c r="I20" t="n">
-        <v>267</v>
-      </c>
-      <c r="J20" t="n">
-        <v>25</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.87354</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-72.6949</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>AURELIO BALDOR</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.86716</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-72.69508</v>
-      </c>
-      <c r="I21" t="n">
-        <v>247</v>
-      </c>
-      <c r="J21" t="n">
-        <v>19</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.86716</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-72.69508</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>FEDERICO VILLARREAL</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.51074</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-73.82404</v>
-      </c>
-      <c r="I22" t="n">
-        <v>280</v>
-      </c>
-      <c r="J22" t="n">
-        <v>15</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.51074</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-73.82404</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
+++ b/ZonasEscolares/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>160531</t>
+          <t>161502</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50226 LA INMACULADA</t>
+          <t>50847</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.863071</t>
+          <t>-12.608377</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-72.6953</t>
+          <t>-72.946645</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>160545</t>
+          <t>160885</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50227 SAN FRANCISCO JAVIER</t>
+          <t>BUEN MAESTRO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.85715</t>
+          <t>-12.86731</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-72.69539</t>
+          <t>-72.69571</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>265</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>160574</t>
+          <t>160791</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50230</t>
+          <t>51076</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.868114</t>
+          <t>-12.86838</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-72.691863</t>
+          <t>-72.69906</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>160630</t>
+          <t>600016</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50236 SANTA ANA</t>
+          <t>PITIRINKENI</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.87124</t>
+          <t>-12.243557</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-72.693727</t>
+          <t>-73.866653</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>160772</t>
+          <t>862211</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>51027 JUAN DE LA CRUZ MONTES SALAS</t>
+          <t>FEDERICO VILLARREAL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.862064</t>
+          <t>-12.51074</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-72.692349</t>
+          <t>-73.82404</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>280</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>160786</t>
+          <t>160809</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>51028 EL ROSARIO</t>
+          <t>501156 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.868313</t>
+          <t>-12.88148</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-72.69593</t>
+          <t>-72.69315</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>254</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>160791</t>
+          <t>783515</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>51076</t>
+          <t>AURELIO BALDOR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.86838</t>
+          <t>-12.86716</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-72.69906</t>
+          <t>-72.69508</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>160809</t>
+          <t>394766</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>501156 SAGRADO CORAZON DE JESUS</t>
+          <t>RIQCHARIY WAYNA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.88148</t>
+          <t>-12.629164</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-72.69315</t>
+          <t>-72.974719</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>160847</t>
+          <t>160574</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>INA 67</t>
+          <t>50230</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.856707</t>
+          <t>-12.868114</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-72.69593</t>
+          <t>-72.691863</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>348</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>160852</t>
+          <t>160786</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LA CONVENCION</t>
+          <t>51028 EL ROSARIO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.857625</t>
+          <t>-12.868313</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-72.693555</t>
+          <t>-72.69593</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>473</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>160866</t>
+          <t>160847</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MANCO II</t>
+          <t>INA 67</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.865258</t>
+          <t>-12.856707</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-72.692337</t>
+          <t>-72.69593</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>209</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>160885</t>
+          <t>717238</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BUEN MAESTRO</t>
+          <t>TALENTOS DE PITAGORAS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.86731</t>
+          <t>-12.87354</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-72.69571</t>
+          <t>-72.6949</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>267</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>160994</t>
+          <t>163855</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LA SALLE</t>
+          <t>50985 ALTO SALKANTAY</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.86231</t>
+          <t>-13.228343</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-72.69904</t>
+          <t>-72.628621</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>209</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>161502</t>
+          <t>160545</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>50847</t>
+          <t>50227 SAN FRANCISCO JAVIER</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.608377</t>
+          <t>-12.85715</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-72.946645</t>
+          <t>-72.69539</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>378</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>163544</t>
+          <t>160994</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>LA SALLE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.7931</t>
+          <t>-12.86231</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-73.6217</t>
+          <t>-72.69904</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>665</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>163855</t>
+          <t>163544</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>50985 ALTO SALKANTAY</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-13.228343</t>
+          <t>-12.7931</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-72.628621</t>
+          <t>-73.6217</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>638</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>394766</t>
+          <t>160531</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RIQCHARIY WAYNA</t>
+          <t>50226 LA INMACULADA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.629164</t>
+          <t>-12.863071</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-72.974719</t>
+          <t>-72.6953</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>707</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>600016</t>
+          <t>160630</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PITIRINKENI</t>
+          <t>50236 SANTA ANA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.243557</t>
+          <t>-12.87124</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-73.866653</t>
+          <t>-72.693727</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>883</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>717238</t>
+          <t>160852</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TALENTOS DE PITAGORAS</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.87354</t>
+          <t>-12.857625</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-72.6949</t>
+          <t>-72.693555</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>800</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>783515</t>
+          <t>160866</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AURELIO BALDOR</t>
+          <t>MANCO II</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.86716</t>
+          <t>-12.865258</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-72.69508</t>
+          <t>-72.692337</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>953</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>862211</t>
+          <t>160772</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FEDERICO VILLARREAL</t>
+          <t>51027 JUAN DE LA CRUZ MONTES SALAS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.51074</t>
+          <t>-12.862064</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-73.82404</t>
+          <t>-72.692349</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">

--- a/ZonasEscolares/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
+++ b/ZonasEscolares/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>161502</t>
+          <t>862211</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50847</t>
+          <t>FEDERICO VILLARREAL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.608377</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-72.946645</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-12.51074</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-73.82404</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>160885</t>
+          <t>783515</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BUEN MAESTRO</t>
+          <t>AURELIO BALDOR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.86731</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-72.69571</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>-12.86716</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-72.69508</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>160791</t>
+          <t>717238</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51076</t>
+          <t>TALENTOS DE PITAGORAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.86838</t>
+          <t>267</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-72.69906</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-12.87354</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-72.6949</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -697,22 +697,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>-12.243557</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>-73.866653</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>862211</t>
+          <t>394766</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FEDERICO VILLARREAL</t>
+          <t>RIQCHARIY WAYNA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.51074</t>
+          <t>242</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-73.82404</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>-12.629164</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-72.974719</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>160809</t>
+          <t>163855</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>501156 SAGRADO CORAZON DE JESUS</t>
+          <t>50985 ALTO SALKANTAY</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.88148</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-72.69315</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>-13.228343</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-72.628621</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>783515</t>
+          <t>163544</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AURELIO BALDOR</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.86716</t>
+          <t>638</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-72.69508</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>-12.7931</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-73.6217</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>394766</t>
+          <t>161502</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RIQCHARIY WAYNA</t>
+          <t>50847</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.629164</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-72.974719</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>-12.608377</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-72.946645</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>160574</t>
+          <t>160994</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50230</t>
+          <t>LA SALLE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.868114</t>
+          <t>665</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-72.691863</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>-12.86231</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-72.69904</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>160786</t>
+          <t>160885</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>51028 EL ROSARIO</t>
+          <t>BUEN MAESTRO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.868313</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-72.69593</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>-12.86731</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-72.69571</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>160847</t>
+          <t>160866</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>INA 67</t>
+          <t>MANCO II</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.856707</t>
+          <t>953</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-72.69593</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-12.865258</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-72.692337</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>717238</t>
+          <t>160852</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TALENTOS DE PITAGORAS</t>
+          <t>LA CONVENCION</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.87354</t>
+          <t>800</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-72.6949</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>-12.857625</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-72.693555</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>163855</t>
+          <t>160847</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>50985 ALTO SALKANTAY</t>
+          <t>INA 67</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-13.228343</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-72.628621</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-12.856707</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-72.69593</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>160545</t>
+          <t>160809</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>50227 SAN FRANCISCO JAVIER</t>
+          <t>501156 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.85715</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-72.69539</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>-12.88148</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-72.69315</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>160994</t>
+          <t>160791</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LA SALLE</t>
+          <t>51076</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.86231</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-72.69904</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>-12.86838</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-72.69906</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>163544</t>
+          <t>160786</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>51028 EL ROSARIO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.7931</t>
+          <t>473</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-73.6217</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>-12.868313</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-72.69593</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>160531</t>
+          <t>160772</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>50226 LA INMACULADA</t>
+          <t>51027 JUAN DE LA CRUZ MONTES SALAS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.863071</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-72.6953</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>-12.862064</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-72.692349</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1565,22 +1565,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>883</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>-12.87124</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>-72.693727</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>883</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>50</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>160852</t>
+          <t>160574</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LA CONVENCION</t>
+          <t>50230</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.857625</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-72.693555</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>-12.868114</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-72.691863</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>160866</t>
+          <t>160545</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MANCO II</t>
+          <t>50227 SAN FRANCISCO JAVIER</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.865258</t>
+          <t>378</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-72.692337</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>-12.85715</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-72.69539</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>160772</t>
+          <t>160531</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>51027 JUAN DE LA CRUZ MONTES SALAS</t>
+          <t>50226 LA INMACULADA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.862064</t>
+          <t>707</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-72.692349</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>-12.863071</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-72.6953</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">

--- a/ZonasEscolares/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
+++ b/ZonasEscolares/excels/CUSCO-LA_CONVENCION-SANTA_ANA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
